--- a/快乐羊毛系统/功能测试需要的文件2026.03.17/最终版测试用例/自动化UI测试需要用到的测试用例3.20/品牌管理/品牌搜索.xlsx
+++ b/快乐羊毛系统/功能测试需要的文件2026.03.17/最终版测试用例/自动化UI测试需要用到的测试用例3.20/品牌管理/品牌搜索.xlsx
@@ -323,7 +323,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,13 +342,6 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -822,148 +815,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1351,7 +1344,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="85" customHeight="1" spans="1:5">
+    <row r="2" ht="34" customHeight="1" spans="1:5">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -1368,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="85" customHeight="1" spans="1:5">
+    <row r="3" ht="34" customHeight="1" spans="1:5">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1385,7 +1378,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" ht="85" customHeight="1" spans="1:5">
+    <row r="4" ht="34" customHeight="1" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1402,7 +1395,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="85" customHeight="1" spans="1:5">
+    <row r="5" ht="34" customHeight="1" spans="1:5">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -1419,7 +1412,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" ht="85" customHeight="1" spans="1:5">
+    <row r="6" ht="34" customHeight="1" spans="1:5">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -1436,7 +1429,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" ht="85" customHeight="1" spans="1:5">
+    <row r="7" ht="34" customHeight="1" spans="1:5">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -1453,7 +1446,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" ht="85" customHeight="1" spans="1:5">
+    <row r="8" ht="34" customHeight="1" spans="1:5">
       <c r="A8" s="3" t="s">
         <v>27</v>
       </c>
@@ -1470,7 +1463,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" ht="85" customHeight="1" spans="1:5">
+    <row r="9" ht="34" customHeight="1" spans="1:5">
       <c r="A9" s="3" t="s">
         <v>31</v>
       </c>
@@ -1487,7 +1480,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" ht="85" customHeight="1" spans="1:5">
+    <row r="10" ht="34" customHeight="1" spans="1:5">
       <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
@@ -1504,7 +1497,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" ht="85" customHeight="1" spans="1:5">
+    <row r="11" ht="34" customHeight="1" spans="1:5">
       <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
@@ -1521,7 +1514,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" ht="85" customHeight="1" spans="1:5">
+    <row r="12" ht="34" customHeight="1" spans="1:5">
       <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
@@ -1538,7 +1531,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" ht="85" customHeight="1" spans="1:5">
+    <row r="13" ht="34" customHeight="1" spans="1:5">
       <c r="A13" s="3" t="s">
         <v>46</v>
       </c>
@@ -1555,7 +1548,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" ht="85" customHeight="1" spans="1:5">
+    <row r="14" ht="34" customHeight="1" spans="1:5">
       <c r="A14" s="3" t="s">
         <v>51</v>
       </c>
@@ -1572,7 +1565,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" ht="85" customHeight="1" spans="1:5">
+    <row r="15" ht="34" customHeight="1" spans="1:5">
       <c r="A15" s="3" t="s">
         <v>51</v>
       </c>
@@ -1589,7 +1582,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" ht="85" customHeight="1" spans="1:5">
+    <row r="16" ht="34" customHeight="1" spans="1:5">
       <c r="A16" s="3" t="s">
         <v>51</v>
       </c>
@@ -1606,7 +1599,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" ht="85" customHeight="1" spans="1:5">
+    <row r="17" ht="34" customHeight="1" spans="1:5">
       <c r="A17" s="3" t="s">
         <v>51</v>
       </c>
@@ -1623,7 +1616,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" ht="85" customHeight="1" spans="1:5">
+    <row r="18" ht="34" customHeight="1" spans="1:5">
       <c r="A18" s="3" t="s">
         <v>51</v>
       </c>
@@ -1640,7 +1633,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" ht="85" customHeight="1" spans="1:5">
+    <row r="19" ht="34" customHeight="1" spans="1:5">
       <c r="A19" s="3" t="s">
         <v>51</v>
       </c>
@@ -1657,7 +1650,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" ht="85" customHeight="1" spans="1:5">
+    <row r="20" ht="34" customHeight="1" spans="1:5">
       <c r="A20" s="3" t="s">
         <v>70</v>
       </c>
@@ -1674,7 +1667,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" ht="85" customHeight="1" spans="1:5">
+    <row r="21" ht="34" customHeight="1" spans="1:5">
       <c r="A21" s="3" t="s">
         <v>70</v>
       </c>
